--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Dialog/dialog.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Dialog/dialog.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="general" sheetId="1" state="visible" r:id="rId3"/>
@@ -1590,8 +1590,8 @@
 While poisoned, bleeding, or paralyzed, your opponent won't regenerate. 
 The cubes will not split when they have bad conditions.
 You can use a scroll of reconstruction to an artifact to re-create the artifact.
-You can prevent getting dimmed by increaseing your resistance to sound.
-You can prevent getting insane by increaseing your resistance to mind.
+You can prevent getting dimmed by increasing your resistance to sound.
+You can prevent getting insane by increasing your resistance to mind.
 Blessing a rod is a good idea. But the effects of blessed rods are less dramatic than blessed potions or scrolls.
 When you are wet, fire damages won't be a problem but electric damages will be a serious threat.
 If you vomit too much in a short period, you will suffer anorexia. When you get anoerxia, don't eat. Just drink potions and water.
@@ -1714,7 +1714,15 @@
     <t xml:space="preserve">bottle</t>
   </si>
   <si>
-    <t xml:space="preserve">류시아|돌아오지 못할 배|누가 이 병을 찾게 됐을 때 쯤엔, 난 이미 바닷속에 가라앉았겠지. 그래도 하늘은 너무나도 파랬어.
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">류시아|돌아오지 못할 배|누가 이 병을 찾게 됐을 때 쯤엔, 난 이미 바닷속에 가라앉았겠지. 그래도 하늘은 너무나도 파랬어.
 이름 없는 병사|최후의 편지|검보다 무거운 건 공포였다. 그래도 난 도망치지 않았다는 걸, 누군가는 알아줬으면 한다.
 에르네스|파도 소리의 기도|신이시여, 파도를 잠재울 힘이 없으시다면, 적어도 제게 잠을 주소서.
 밀레이유|약속의 해변|먼저 도착하면 불을 피우고 기다릴게. 헤매지 말고 와.
@@ -1735,7 +1743,20 @@
 소녀|첫 여행|조금 무서워. 그치만 즐거워.
 누군가|이걸 주운 사람에게|당신이 이걸 읽고 있다면, 세계는 아직 계속되고 있다는 것이다.
 불명|지…|집… 돌아갈래…!
-불명|이…|이 편지는 에우다나에서 최초로 시작되어 일년에 한바퀴를 돌면서 받는 사람에게 행운을 주었고 지금은 당신에게로 옮겨진 이 편지는 4일 안에 당신 곁을 떠나야 합니다. 이 편지를 포함해서 7통을 행운이 필요한 사람에게…</t>
+불명|이…|이 편지는 에우다나에서 최초로 시작되어 일년에 한바퀴를 돌면서 받는 사람에게 행운을 주었고 지금은 당신에게로 옮겨진 이 편지는 4일 안에 당신 곁을 떠나야 합니다. 이 편지를 포함해서 7통을 행운이 필요한 사람에게…
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">해적왕|보물|찾아라! 이 세상 전부를 그곳에 두고 왔으니까!
+해적|두고봐!|난 해적왕이 될 거야!!</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">リュシア|帰らぬ船|この瓶が誰かの手に届くなら、私はもう海の底でしょう。けれど空はとても青かった。
@@ -1759,7 +1780,9 @@
 少女|はじめての旅|少し怖い。でも楽しい。
 誰か|拾ったあなたへ|あなたがこれを読んでいるなら、世界はまだ続いている。
 不明|お…|おうち…かえう…！
-不明|もう…|もうだめぽ</t>
+不明|もう…|もうだめぽ
+海賊王|財宝| 探せ！ この世の全てをそこに置いてきた！
+海賊|見てろ！| 海賊王に、おれはなる ！！</t>
   </si>
   <si>
     <t xml:space="preserve">Lucia|The Ship That Never Returned|If this bottle reaches someone, I will likely be beneath the sea by then. But the sky was very blue.
@@ -1783,7 +1806,9 @@
 Little Girl|My First Journey|I'm a little scared. But it's fun.
 Someone|To Whoever Finds This|If you are reading this, the world is still going on.
 Unknown|I...|I'm...going...home...!
-Unknown|I'm...|Moudamepo</t>
+Unknown|I'm...|Moudamepo
+Pirate King|My treasure?|Find it! I left everything in this world there!
+Pirate|Watch me|I’m gonna be King of the Pirates!!</t>
   </si>
   <si>
     <t xml:space="preserve">mysilia</t>
@@ -2237,7 +2262,7 @@
 How long has that warmonger's altar been here?
 It seems my old body still remains on the surface.
 Surely you do not believe that gods are omnipotent?
-You are free to believe that the world has a purpose, but do not expect too much from its designer's competenc </t>
+You are free to believe that the world has a purpose, but do not expect too much from its designer's competence.</t>
   </si>
   <si>
     <t xml:space="preserve">mamani2</t>
@@ -2520,7 +2545,7 @@
 弱きを助け、悪を砕くのだ！</t>
   </si>
   <si>
-    <t xml:space="preserve">Muwahahaha! ...What are you?
+    <t xml:space="preserve">Muwahahaha! ...What?
 By Opatos, I'll squash every bad bug that gets near Princess Stasha! Muwahaha!
 Long live Princess Stasha!
 I wish I was in the war 15 years ago!
@@ -4109,7 +4134,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -4148,6 +4173,13 @@
       <name val="ＭＳ Ｐゴシック"/>
       <family val="0"/>
       <charset val="128"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="129"/>
     </font>
     <font>
       <sz val="10"/>
@@ -4255,15 +4287,15 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4354,9 +4386,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>38</xdr:col>
-      <xdr:colOff>272160</xdr:colOff>
+      <xdr:colOff>270720</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>110880</xdr:rowOff>
+      <xdr:rowOff>109440</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -4366,7 +4398,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="49651560" cy="110880"/>
+          <a:ext cx="49650120" cy="109440"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5797,7 +5829,7 @@
   <sheetFormatPr defaultColWidth="11.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="6" width="13.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="6" width="10.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="6" width="71.48"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="6" width="117.64"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="6" width="122.68"/>
   </cols>
@@ -6092,7 +6124,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="231.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="252.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
         <v>430</v>
       </c>
@@ -6289,7 +6321,7 @@
       <c r="A15" s="3" t="s">
         <v>474</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="3" t="s">
         <v>475</v>
       </c>
       <c r="C15" s="3" t="s">
@@ -6303,7 +6335,7 @@
       <c r="A16" s="3" t="s">
         <v>478</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="5" t="s">
         <v>479</v>
       </c>
       <c r="C16" s="3" t="s">
@@ -6317,7 +6349,7 @@
       <c r="A17" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="5" t="s">
         <v>483</v>
       </c>
       <c r="C17" s="3" t="s">
@@ -6347,8 +6379,8 @@
   <sheetFormatPr defaultColWidth="11.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="71.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="85.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="110.96"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="139.81"/>
   </cols>
   <sheetData>
@@ -6519,7 +6551,7 @@
       <c r="A15" s="1" t="s">
         <v>523</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="1" t="s">
         <v>524</v>
       </c>
       <c r="C15" s="3" t="s">

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Dialog/dialog.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Dialog/dialog.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="general" sheetId="1" state="visible" r:id="rId3"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="728" uniqueCount="702">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="732" uniqueCount="706">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -1714,15 +1714,7 @@
     <t xml:space="preserve">bottle</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">류시아|돌아오지 못할 배|누가 이 병을 찾게 됐을 때 쯤엔, 난 이미 바닷속에 가라앉았겠지. 그래도 하늘은 너무나도 파랬어.
+    <t xml:space="preserve">류시아|돌아오지 못할 배|누가 이 병을 찾게 됐을 때 쯤엔, 난 이미 바닷속에 가라앉았겠지. 그래도 하늘은 너무나도 파랬어.
 이름 없는 병사|최후의 편지|검보다 무거운 건 공포였다. 그래도 난 도망치지 않았다는 걸, 누군가는 알아줬으면 한다.
 에르네스|파도 소리의 기도|신이시여, 파도를 잠재울 힘이 없으시다면, 적어도 제게 잠을 주소서.
 밀레이유|약속의 해변|먼저 도착하면 불을 피우고 기다릴게. 헤매지 말고 와.
@@ -1744,19 +1736,8 @@
 누군가|이걸 주운 사람에게|당신이 이걸 읽고 있다면, 세계는 아직 계속되고 있다는 것이다.
 불명|지…|집… 돌아갈래…!
 불명|이…|이 편지는 에우다나에서 최초로 시작되어 일년에 한바퀴를 돌면서 받는 사람에게 행운을 주었고 지금은 당신에게로 옮겨진 이 편지는 4일 안에 당신 곁을 떠나야 합니다. 이 편지를 포함해서 7통을 행운이 필요한 사람에게…
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">해적왕|보물|찾아라! 이 세상 전부를 그곳에 두고 왔으니까!
+해적왕|보물|찾아라! 이 세상 전부를 그곳에 두고 왔으니까!
 해적|두고봐!|난 해적왕이 될 거야!!</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">リュシア|帰らぬ船|この瓶が誰かの手に届くなら、私はもう海の底でしょう。けれど空はとても青かった。
@@ -2215,6 +2196,100 @@
 Our great father oversees our penance, and there is no escape from our fates.
 As time passes, we grow less concerned with our material conditions...
 Yes #race, you're standing in front of an exile who has lived more than 1000 years.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">oldkeep</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">이 성은 불야성이라고 불리고 있{어}.
+성의 첨탑에서는 밤이면 밤마다 광란의 연회가 벌어지고 있는 모양{이다}.
+{I}도 와이난 공의 연회에 초대받아 보고 {싶다}!
+와이난님의 어머님은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">… 음, 아주 기발한 센스를 가진 예술가{다}.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">조각상이랑 그림들이 쳐다보고 있는 것 같{네}. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">기분 탓{이지}?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">정말 훌륭한 아트들{이다}!
+마지막으로 와이난님과 그 어머님의 모습을 본 게, 대체 몇 년 전{이지}?
+이 고성은 티리스 10경 중 하나로 꼽히고 있{어}.
+가레스는 정말 답도 없는 쓰레기{다}.
+가레스는 진짜 쓰레기 자식{이다}. 그런 놈들이 있으니까 이 세상이 어지러운 {거야}.
+어디로 가도 달콤한 장미 향이 끊이질 {않아}!
+저 조각상, 내가 아는 사람이랑 꼭 닮았{네}.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">この城は不夜城と呼ばれて{いる}。
+城の尖塔では、夜な夜な狂宴が繰り広げられているそう{だ}。
+私もワイナン公の宴に招かれてみたいもの{だ}！
+ワイナン様の母上は…そう、とても奇抜なセンスを持った芸術家{だ}。
+気のせい{かな}？彫像や絵画に見られている気がする{のだ}。
+実にすばらしいアートの数々{だ}！
+最後にワイナン様と母上の姿を見たのは、もう何年前だろう{か}？
+この古城は、ティリス十景のひとつに数えられている{のだ}。
+ガレスは本当にろくでもないクズ{だ}。
+ガレスは正真正銘のクソったれ{だ}。あんな奴がいるから世の中おかしくなる{のだ}。
+どこにいっても薔薇の甘い香りが漂ってくる{のだ}！
+あの彫像、私の知り合いとそっくり{だ}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This castle is known as the Nevernight Castle.
+They say wild revelries take place in the castle's spires night after night.
+I'd love to be invited to one of Lord Wynan's banquets someday!
+The Lady Mother is... well, an artist with a very eccentric sense of style.
+Is it just me? I feel like the statues and paintings are watching me.
+What a magnificent collection of art!
+How many years has it been since anyone last saw Lord Wynan and the Lady Mother?
+This ancient castle is counted among the Ten Scenic Wonders of Tyris.
+Gareth is a truly rotten bastard.
+Gareth is a complete asshole. It's scum like him that makes the world such a messed-up place.
+The sweet scent of roses fills the air wherever you go!
+That statue looks exactly like someone I know.</t>
   </si>
   <si>
     <t xml:space="preserve">mimu</t>
@@ -4134,7 +4209,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -4177,21 +4252,28 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="游ゴシック"/>
       <family val="2"/>
       <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="0"/>
+      <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
@@ -4250,7 +4332,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -4287,12 +4369,16 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -4386,9 +4472,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>38</xdr:col>
-      <xdr:colOff>270720</xdr:colOff>
+      <xdr:colOff>270360</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>109440</xdr:rowOff>
+      <xdr:rowOff>109080</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -4398,7 +4484,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="49650120" cy="109440"/>
+          <a:ext cx="49649760" cy="109080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5829,7 +5915,7 @@
   <sheetFormatPr defaultColWidth="11.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="6" width="13.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="6" width="71.48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="6" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="6" width="117.64"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="6" width="122.68"/>
   </cols>
@@ -6154,11 +6240,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr defaultColWidth="11.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15.7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="81.48"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="109.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="123.06"/>
   </cols>
@@ -6307,7 +6393,7 @@
       <c r="A14" s="3" t="s">
         <v>470</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="3" t="s">
         <v>471</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -6321,7 +6407,7 @@
       <c r="A15" s="3" t="s">
         <v>474</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="5" t="s">
         <v>475</v>
       </c>
       <c r="C15" s="3" t="s">
@@ -6349,7 +6435,7 @@
       <c r="A17" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="3" t="s">
         <v>483</v>
       </c>
       <c r="C17" s="3" t="s">
@@ -6357,6 +6443,20 @@
       </c>
       <c r="D17" s="3" t="s">
         <v>485</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="9" t="s">
+        <v>486</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>489</v>
       </c>
     </row>
   </sheetData>
@@ -6409,660 +6509,660 @@
     </row>
     <row r="5" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="9" t="s">
-        <v>503</v>
+      <c r="A10" s="11" t="s">
+        <v>507</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>523</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>524</v>
+        <v>527</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>528</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="355.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="44.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="56.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="79.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="44.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="179.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="9" t="s">
-        <v>599</v>
+      <c r="A34" s="11" t="s">
+        <v>603</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="9" t="s">
-        <v>602</v>
+      <c r="A35" s="11" t="s">
+        <v>606</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>603</v>
-      </c>
-      <c r="C35" s="11" t="s">
-        <v>604</v>
+        <v>607</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>608</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="9" t="s">
-        <v>606</v>
+      <c r="A36" s="11" t="s">
+        <v>610</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>607</v>
-      </c>
-      <c r="C36" s="12" t="s">
-        <v>608</v>
+        <v>611</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>612</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="3" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="9" t="s">
-        <v>642</v>
+      <c r="A45" s="11" t="s">
+        <v>646</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="9" t="s">
-        <v>646</v>
+      <c r="A46" s="11" t="s">
+        <v>650</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="9" t="s">
-        <v>650</v>
+      <c r="A47" s="11" t="s">
+        <v>654</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="9" t="s">
-        <v>654</v>
+      <c r="A48" s="11" t="s">
+        <v>658</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="9" t="s">
-        <v>658</v>
+      <c r="A49" s="11" t="s">
+        <v>662</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="9" t="s">
-        <v>662</v>
+      <c r="A50" s="11" t="s">
+        <v>666</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
     </row>
   </sheetData>
@@ -7115,114 +7215,114 @@
     </row>
     <row r="5" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="168.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="220.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="231.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="210.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="314.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="112.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>697</v>
+        <v>701</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="199.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="9" t="s">
-        <v>698</v>
+      <c r="A12" s="11" t="s">
+        <v>702</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
     </row>
   </sheetData>
